--- a/AAII_Financials/Yearly/SITC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SITC_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>SITC</t>
   </si>
@@ -656,183 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>546300</v>
+      </c>
+      <c r="E8" s="3">
         <v>552400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>532900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>460300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>508000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>707300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>921600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1005800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1028100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>985700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>829900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>800400</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>165700</v>
+      </c>
+      <c r="E9" s="3">
         <v>170000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>152800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>138400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>139700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>208000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>250900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>277100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>293700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>281100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>239200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>233100</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>380600</v>
+      </c>
+      <c r="E10" s="3">
         <v>382400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>380100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>321900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>368300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>499300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>670700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>728700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>734400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>704600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>590800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>567300</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +860,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -886,9 +899,12 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,87 +941,96 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-43000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-11900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-21900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>176400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>414400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>107600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>282600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>72100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>26400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>159200</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>212500</v>
+      </c>
+      <c r="E15" s="3">
         <v>203500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>185800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>170700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>165100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>242100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>346200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>389500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>402000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>402800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>296600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>248800</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,86 +1043,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>425300</v>
+      </c>
+      <c r="E17" s="3">
         <v>377000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>381700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>340100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>367100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>692800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1101400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>850300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1051800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>840500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>641700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>717500</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E18" s="3">
         <v>175300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>151200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>120200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>140900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-179800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>155500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-23700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>145100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>188200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>82900</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1113,203 +1145,219 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>228800</v>
+      </c>
+      <c r="E20" s="3">
         <v>72000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>52200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>46400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>18400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-23400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>51700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>33800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>115000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>50300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>124900</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>562200</v>
+      </c>
+      <c r="E21" s="3">
         <v>450800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>389100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>286000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>352300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>275000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>143000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>596700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>412200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>679200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>562600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>458900</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E22" s="3">
         <v>77700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>76400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>77600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>84700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>141300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>188600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>217600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>241700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>237100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>214400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>221400</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>267800</v>
+      </c>
+      <c r="E23" s="3">
         <v>169600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>127000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>37700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>102500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-108400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-391900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-231600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>24100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13600</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1346,87 +1394,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>265700</v>
+      </c>
+      <c r="E26" s="3">
         <v>168800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>125400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>36600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>101800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-109300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-404300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-237900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14800</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>253900</v>
+      </c>
+      <c r="E27" s="3">
         <v>157100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>105600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>60600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-145600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-432600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-36500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-263400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-43900</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1463,9 +1520,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1481,30 +1541,33 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3">
         <v>225400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>161200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>73400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>167600</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>93800</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-31000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-16400</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,9 +1604,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1580,87 +1646,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-228800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-72000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-52200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-46400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-18400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>23400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-51700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-33800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-115000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-50300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-124900</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>253900</v>
+      </c>
+      <c r="E33" s="3">
         <v>157100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>105600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>60600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>79800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-271400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>36900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-95800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>89600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-44500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-60300</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1697,92 +1772,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>253900</v>
+      </c>
+      <c r="E35" s="3">
         <v>157100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>105600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>60600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>79800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-271400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>36900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-95800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>89600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-44500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-60300</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1798,8 +1882,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1815,47 +1900,51 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>552000</v>
+      </c>
+      <c r="E41" s="3">
         <v>20300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>41800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>69700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>92600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>22400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>86700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>31200</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1892,48 +1981,54 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E43" s="3">
         <v>63900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>61800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>74000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>61700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>67300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>167300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>121400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>129100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>132700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>129500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>126200</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1970,48 +2065,54 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E45" s="3">
         <v>6700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12500</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2048,126 +2149,138 @@
       <c r="N46" s="3">
         <v>0</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E47" s="3">
         <v>44600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>64600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>267300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>492100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>573300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>403500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>503600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>510300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>471100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>526300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>692300</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3278200</v>
+      </c>
+      <c r="E48" s="3">
         <v>3798500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3686400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3582900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3442500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3455500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6294500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7247900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8065300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8426200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18147000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6968400</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E49" s="3">
         <v>79700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>87400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>85400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>54300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>73400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>172400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>228700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>295100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>389200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>409600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>129300</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2204,9 +2317,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2243,48 +2359,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E52" s="3">
         <v>8500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>45300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>122400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>66200</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2321,48 +2443,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4061400</v>
+      </c>
+      <c r="E54" s="3">
         <v>4045000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3967100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4108300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4093600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4206300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7170100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8197500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9097100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9519400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9693100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8055800</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2378,8 +2506,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2395,47 +2524,51 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>158600</v>
+      </c>
+      <c r="E57" s="3">
         <v>177200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>180300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>175300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>180100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>203700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>344800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>382300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>425500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>448200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>415400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>326000</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2472,48 +2605,54 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100900</v>
+      </c>
+      <c r="E59" s="3">
         <v>68200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>66700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>54600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>84800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>45300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>78500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>75200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>68600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>61500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>55100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>44200</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2550,48 +2689,54 @@
       <c r="N60" s="3">
         <v>0</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1626300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1707000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1677400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1933500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1847300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1884400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3849300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4494000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5139500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5212200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5294700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4319100</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2628,9 +2773,12 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2667,9 +2815,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2706,9 +2857,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2745,48 +2899,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1885800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1958200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1930200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2166800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2115200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2136300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4279100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4960000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5641900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5749200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5788400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4713700</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2802,8 +2962,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2840,9 +3001,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2879,9 +3043,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2892,19 +3059,19 @@
         <v>175000</v>
       </c>
       <c r="F70" s="3">
-        <v>325000</v>
+        <v>175000</v>
       </c>
       <c r="G70" s="3">
         <v>325000</v>
       </c>
       <c r="H70" s="3">
-        <v>525000</v>
+        <v>325000</v>
       </c>
       <c r="I70" s="3">
         <v>525000</v>
       </c>
       <c r="J70" s="3">
-        <v>350000</v>
+        <v>525000</v>
       </c>
       <c r="K70" s="3">
         <v>350000</v>
@@ -2913,14 +3080,17 @@
         <v>350000</v>
       </c>
       <c r="M70" s="3">
-        <v>405000</v>
+        <v>350000</v>
       </c>
       <c r="N70" s="3">
         <v>405000</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>405000</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2957,48 +3127,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3934700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-4046400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-4092800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-4099500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4066100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3980200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3183100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2632300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2391800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2047200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1915600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1694800</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3035,9 +3211,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3074,9 +3253,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3113,48 +3295,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2000500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1911800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1861900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1616500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1653400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1545100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2365900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2887500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3105200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3420200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3499700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2937100</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3191,92 +3379,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>253900</v>
+      </c>
+      <c r="E81" s="3">
         <v>157100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>105600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>60600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>79800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-271400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>36900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-95800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>89600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-44500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-60300</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3292,47 +3489,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>212500</v>
+      </c>
+      <c r="E83" s="3">
         <v>203500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>185800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>170700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>165100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>242100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>346200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>389500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>402000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>419100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>324100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>251100</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3369,9 +3570,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3408,9 +3612,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3447,9 +3654,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3486,9 +3696,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3525,48 +3738,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>238500</v>
+      </c>
+      <c r="E89" s="3">
         <v>257300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>282500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>190200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>270200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>263400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>410400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>460700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>433500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>420300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>374000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>304200</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3582,47 +3801,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-272800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-449900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-207100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-63800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-185000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-158600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-201400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-308900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-481700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-591800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1068500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-586900</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3659,9 +3882,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3698,48 +3924,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>559900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-167600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>74500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>102500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>818300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>478600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>473000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-54600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>153200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-897900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-588400</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3755,47 +3987,51 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-120500</v>
+      </c>
+      <c r="E96" s="3">
         <v>-120000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-99500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-98300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-180700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-281300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-305800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-293900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-265300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-240600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-194500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-154800</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3832,9 +4068,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3871,9 +4110,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3910,48 +4152,54 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-250600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-111700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-388100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-237400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-254300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1162800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-833500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-927000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-378800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-638600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>579300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>274800</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3977,57 +4225,63 @@
         <v>0</v>
       </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>547800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-22000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-31200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>55300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-81100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>55500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-65700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>55500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10000</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SITC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SITC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>SITC</t>
   </si>
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>546300</v>
+        <v>550900</v>
       </c>
       <c r="E8" s="3">
-        <v>552400</v>
+        <v>574600</v>
       </c>
       <c r="F8" s="3">
-        <v>532900</v>
+        <v>582300</v>
       </c>
       <c r="G8" s="3">
-        <v>460300</v>
+        <v>461400</v>
       </c>
       <c r="H8" s="3">
-        <v>508000</v>
+        <v>517800</v>
       </c>
       <c r="I8" s="3">
-        <v>707300</v>
+        <v>698000</v>
       </c>
       <c r="J8" s="3">
-        <v>921600</v>
+        <v>915900</v>
       </c>
       <c r="K8" s="3">
         <v>1005800</v>
@@ -783,7 +783,7 @@
         <v>208000</v>
       </c>
       <c r="J9" s="3">
-        <v>250900</v>
+        <v>263700</v>
       </c>
       <c r="K9" s="3">
         <v>277100</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>380600</v>
+        <v>385100</v>
       </c>
       <c r="E10" s="3">
-        <v>382400</v>
+        <v>404600</v>
       </c>
       <c r="F10" s="3">
-        <v>380100</v>
+        <v>429500</v>
       </c>
       <c r="G10" s="3">
-        <v>321900</v>
+        <v>323000</v>
       </c>
       <c r="H10" s="3">
-        <v>368300</v>
+        <v>378200</v>
       </c>
       <c r="I10" s="3">
-        <v>499300</v>
+        <v>490000</v>
       </c>
       <c r="J10" s="3">
-        <v>670700</v>
+        <v>652200</v>
       </c>
       <c r="K10" s="3">
         <v>728700</v>
@@ -951,25 +951,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-3700</v>
+        <v>-216500</v>
       </c>
       <c r="E14" s="3">
-        <v>-43000</v>
+        <v>-95300</v>
       </c>
       <c r="F14" s="3">
-        <v>-11900</v>
+        <v>-15900</v>
       </c>
       <c r="G14" s="3">
-        <v>-21900</v>
+        <v>-22300</v>
       </c>
       <c r="H14" s="3">
-        <v>4000</v>
+        <v>-14100</v>
       </c>
       <c r="I14" s="3">
-        <v>176400</v>
+        <v>-157900</v>
       </c>
       <c r="J14" s="3">
-        <v>414400</v>
+        <v>249300</v>
       </c>
       <c r="K14" s="3">
         <v>107600</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>425300</v>
+        <v>424000</v>
       </c>
       <c r="E17" s="3">
-        <v>377000</v>
+        <v>420100</v>
       </c>
       <c r="F17" s="3">
-        <v>381700</v>
+        <v>393600</v>
       </c>
       <c r="G17" s="3">
-        <v>340100</v>
+        <v>362000</v>
       </c>
       <c r="H17" s="3">
-        <v>367100</v>
+        <v>363100</v>
       </c>
       <c r="I17" s="3">
-        <v>692800</v>
+        <v>507100</v>
       </c>
       <c r="J17" s="3">
-        <v>1101400</v>
+        <v>669100</v>
       </c>
       <c r="K17" s="3">
         <v>850300</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>121000</v>
+        <v>126800</v>
       </c>
       <c r="E18" s="3">
-        <v>175300</v>
+        <v>154500</v>
       </c>
       <c r="F18" s="3">
-        <v>151200</v>
+        <v>188700</v>
       </c>
       <c r="G18" s="3">
-        <v>120200</v>
+        <v>99500</v>
       </c>
       <c r="H18" s="3">
-        <v>140900</v>
+        <v>154700</v>
       </c>
       <c r="I18" s="3">
-        <v>14500</v>
+        <v>190800</v>
       </c>
       <c r="J18" s="3">
-        <v>-179800</v>
+        <v>246800</v>
       </c>
       <c r="K18" s="3">
         <v>155500</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>228800</v>
+        <v>-2100</v>
       </c>
       <c r="E20" s="3">
-        <v>72000</v>
+        <v>2500</v>
       </c>
       <c r="F20" s="3">
-        <v>52200</v>
+        <v>1200</v>
       </c>
       <c r="G20" s="3">
-        <v>-4900</v>
+        <v>18400</v>
       </c>
       <c r="H20" s="3">
-        <v>46400</v>
+        <v>-400</v>
       </c>
       <c r="I20" s="3">
-        <v>18400</v>
+        <v>110900</v>
       </c>
       <c r="J20" s="3">
-        <v>-23400</v>
+        <v>68000</v>
       </c>
       <c r="K20" s="3">
         <v>51700</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>562200</v>
+        <v>341400</v>
       </c>
       <c r="E21" s="3">
-        <v>450800</v>
+        <v>355500</v>
       </c>
       <c r="F21" s="3">
-        <v>389100</v>
+        <v>373300</v>
       </c>
       <c r="G21" s="3">
-        <v>286000</v>
+        <v>251800</v>
       </c>
       <c r="H21" s="3">
-        <v>352300</v>
+        <v>320200</v>
       </c>
       <c r="I21" s="3">
-        <v>275000</v>
+        <v>322000</v>
       </c>
       <c r="J21" s="3">
-        <v>143000</v>
+        <v>525000</v>
       </c>
       <c r="K21" s="3">
         <v>596700</v>
@@ -1293,10 +1293,10 @@
         <v>102500</v>
       </c>
       <c r="I23" s="3">
-        <v>-108400</v>
+        <v>117000</v>
       </c>
       <c r="J23" s="3">
-        <v>-391900</v>
+        <v>-230700</v>
       </c>
       <c r="K23" s="3">
         <v>-10400</v>
@@ -1419,10 +1419,10 @@
         <v>101800</v>
       </c>
       <c r="I26" s="3">
-        <v>-109300</v>
+        <v>116100</v>
       </c>
       <c r="J26" s="3">
-        <v>-404300</v>
+        <v>-243100</v>
       </c>
       <c r="K26" s="3">
         <v>-12200</v>
@@ -1452,7 +1452,7 @@
         <v>157100</v>
       </c>
       <c r="F27" s="3">
-        <v>105600</v>
+        <v>105500</v>
       </c>
       <c r="G27" s="3">
         <v>15000</v>
@@ -1461,10 +1461,10 @@
         <v>60600</v>
       </c>
       <c r="I27" s="3">
-        <v>-145600</v>
+        <v>79800</v>
       </c>
       <c r="J27" s="3">
-        <v>-432600</v>
+        <v>-271400</v>
       </c>
       <c r="K27" s="3">
         <v>-36500</v>
@@ -1529,26 +1529,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>225400</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>161200</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>73400</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-228800</v>
+        <v>2100</v>
       </c>
       <c r="E32" s="3">
-        <v>-72000</v>
+        <v>-2500</v>
       </c>
       <c r="F32" s="3">
-        <v>-52200</v>
+        <v>-1200</v>
       </c>
       <c r="G32" s="3">
-        <v>4900</v>
+        <v>-18400</v>
       </c>
       <c r="H32" s="3">
-        <v>-46400</v>
+        <v>400</v>
       </c>
       <c r="I32" s="3">
-        <v>-18400</v>
+        <v>-110900</v>
       </c>
       <c r="J32" s="3">
-        <v>23400</v>
+        <v>-68000</v>
       </c>
       <c r="K32" s="3">
         <v>-51700</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>253900</v>
+        <v>265700</v>
       </c>
       <c r="E33" s="3">
-        <v>157100</v>
+        <v>168700</v>
       </c>
       <c r="F33" s="3">
-        <v>105600</v>
+        <v>124900</v>
       </c>
       <c r="G33" s="3">
-        <v>15000</v>
+        <v>35700</v>
       </c>
       <c r="H33" s="3">
-        <v>60600</v>
+        <v>100700</v>
       </c>
       <c r="I33" s="3">
-        <v>79800</v>
+        <v>114400</v>
       </c>
       <c r="J33" s="3">
-        <v>-271400</v>
+        <v>-241700</v>
       </c>
       <c r="K33" s="3">
         <v>36900</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>253900</v>
+        <v>265700</v>
       </c>
       <c r="E35" s="3">
-        <v>157100</v>
+        <v>168700</v>
       </c>
       <c r="F35" s="3">
-        <v>105600</v>
+        <v>124900</v>
       </c>
       <c r="G35" s="3">
-        <v>15000</v>
+        <v>35700</v>
       </c>
       <c r="H35" s="3">
-        <v>60600</v>
+        <v>100700</v>
       </c>
       <c r="I35" s="3">
-        <v>79800</v>
+        <v>114400</v>
       </c>
       <c r="J35" s="3">
-        <v>-271400</v>
+        <v>-241700</v>
       </c>
       <c r="K35" s="3">
         <v>36900</v>
@@ -1997,19 +1997,19 @@
         <v>63900</v>
       </c>
       <c r="F43" s="3">
-        <v>61800</v>
+        <v>61400</v>
       </c>
       <c r="G43" s="3">
-        <v>74000</v>
+        <v>73500</v>
       </c>
       <c r="H43" s="3">
-        <v>61700</v>
+        <v>68100</v>
       </c>
       <c r="I43" s="3">
-        <v>67300</v>
+        <v>121000</v>
       </c>
       <c r="J43" s="3">
-        <v>167300</v>
+        <v>187000</v>
       </c>
       <c r="K43" s="3">
         <v>121400</v>
@@ -2032,26 +2032,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5100</v>
+        <v>32600</v>
       </c>
       <c r="E45" s="3">
-        <v>6700</v>
+        <v>18000</v>
       </c>
       <c r="F45" s="3">
-        <v>7700</v>
+        <v>11500</v>
       </c>
       <c r="G45" s="3">
-        <v>7400</v>
+        <v>11200</v>
       </c>
       <c r="H45" s="3">
-        <v>6100</v>
+        <v>10200</v>
       </c>
       <c r="I45" s="3">
-        <v>5400</v>
+        <v>9800</v>
       </c>
       <c r="J45" s="3">
-        <v>10800</v>
+        <v>15900</v>
       </c>
       <c r="K45" s="3">
         <v>26800</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>667200</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>103200</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>116200</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>159100</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>97500</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>144400</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>297600</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2171,13 +2171,13 @@
         <v>267300</v>
       </c>
       <c r="H47" s="3">
-        <v>492100</v>
+        <v>484600</v>
       </c>
       <c r="I47" s="3">
-        <v>573300</v>
+        <v>519600</v>
       </c>
       <c r="J47" s="3">
-        <v>403500</v>
+        <v>383800</v>
       </c>
       <c r="K47" s="3">
         <v>503600</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>60700</v>
+        <v>69000</v>
       </c>
       <c r="E49" s="3">
-        <v>79700</v>
+        <v>87700</v>
       </c>
       <c r="F49" s="3">
-        <v>87400</v>
+        <v>94100</v>
       </c>
       <c r="G49" s="3">
-        <v>85400</v>
+        <v>90400</v>
       </c>
       <c r="H49" s="3">
-        <v>54300</v>
+        <v>58000</v>
       </c>
       <c r="I49" s="3">
-        <v>73400</v>
+        <v>77400</v>
       </c>
       <c r="J49" s="3">
-        <v>172400</v>
+        <v>182400</v>
       </c>
       <c r="K49" s="3">
         <v>228700</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>22400</v>
+        <v>2300</v>
       </c>
       <c r="E52" s="3">
-        <v>8500</v>
+        <v>3500</v>
       </c>
       <c r="F52" s="3">
-        <v>5600</v>
+        <v>1700</v>
       </c>
       <c r="G52" s="3">
-        <v>10800</v>
+        <v>2300</v>
       </c>
       <c r="H52" s="3">
-        <v>11200</v>
+        <v>3000</v>
       </c>
       <c r="I52" s="3">
-        <v>8300</v>
+        <v>3600</v>
       </c>
       <c r="J52" s="3">
-        <v>10000</v>
+        <v>3900</v>
       </c>
       <c r="K52" s="3">
         <v>13500</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>158600</v>
+        <v>112500</v>
       </c>
       <c r="E57" s="3">
-        <v>177200</v>
+        <v>117400</v>
       </c>
       <c r="F57" s="3">
-        <v>180300</v>
+        <v>120600</v>
       </c>
       <c r="G57" s="3">
-        <v>175300</v>
+        <v>118000</v>
       </c>
       <c r="H57" s="3">
-        <v>180100</v>
+        <v>133100</v>
       </c>
       <c r="I57" s="3">
-        <v>203700</v>
+        <v>153300</v>
       </c>
       <c r="J57" s="3">
-        <v>344800</v>
+        <v>96600</v>
       </c>
       <c r="K57" s="3">
         <v>382300</v>
@@ -2573,7 +2573,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2615,19 +2615,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100900</v>
+        <v>63800</v>
       </c>
       <c r="E59" s="3">
-        <v>68200</v>
+        <v>30400</v>
       </c>
       <c r="F59" s="3">
-        <v>66700</v>
+        <v>28200</v>
       </c>
       <c r="G59" s="3">
-        <v>54600</v>
+        <v>14800</v>
       </c>
       <c r="H59" s="3">
-        <v>84800</v>
+        <v>44000</v>
       </c>
       <c r="I59" s="3">
         <v>45300</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>180800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>147800</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>148800</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>132800</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>177200</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>198600</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>295800</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2699,19 +2699,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1626300</v>
+        <v>1659000</v>
       </c>
       <c r="E61" s="3">
-        <v>1707000</v>
+        <v>1744800</v>
       </c>
       <c r="F61" s="3">
-        <v>1677400</v>
+        <v>1715900</v>
       </c>
       <c r="G61" s="3">
-        <v>1933500</v>
+        <v>1973300</v>
       </c>
       <c r="H61" s="3">
-        <v>1847300</v>
+        <v>1888000</v>
       </c>
       <c r="I61" s="3">
         <v>1884400</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>46100</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>59800</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>59700</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>57300</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>47000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>50300</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>127500</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -2912,22 +2912,22 @@
         <v>1885800</v>
       </c>
       <c r="E66" s="3">
-        <v>1958200</v>
+        <v>1952400</v>
       </c>
       <c r="F66" s="3">
-        <v>1930200</v>
+        <v>1924400</v>
       </c>
       <c r="G66" s="3">
-        <v>2166800</v>
+        <v>2163500</v>
       </c>
       <c r="H66" s="3">
-        <v>2115200</v>
+        <v>2112100</v>
       </c>
       <c r="I66" s="3">
-        <v>2136300</v>
+        <v>2133300</v>
       </c>
       <c r="J66" s="3">
-        <v>4279100</v>
+        <v>4272600</v>
       </c>
       <c r="K66" s="3">
         <v>4960000</v>
@@ -3136,26 +3136,26 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-3934700</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-4046400</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-4092800</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-4099500</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-4066100</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-3980200</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-3183100</v>
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K72" s="3">
         <v>-2632300</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>253900</v>
+        <v>265700</v>
       </c>
       <c r="E81" s="3">
-        <v>157100</v>
+        <v>168700</v>
       </c>
       <c r="F81" s="3">
-        <v>105600</v>
+        <v>124900</v>
       </c>
       <c r="G81" s="3">
-        <v>15000</v>
+        <v>35700</v>
       </c>
       <c r="H81" s="3">
-        <v>60600</v>
+        <v>100700</v>
       </c>
       <c r="I81" s="3">
-        <v>79800</v>
+        <v>114400</v>
       </c>
       <c r="J81" s="3">
-        <v>-271400</v>
+        <v>-241700</v>
       </c>
       <c r="K81" s="3">
         <v>36900</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>212500</v>
+        <v>189800</v>
       </c>
       <c r="E83" s="3">
-        <v>203500</v>
+        <v>176000</v>
       </c>
       <c r="F83" s="3">
-        <v>185800</v>
+        <v>164200</v>
       </c>
       <c r="G83" s="3">
-        <v>170700</v>
+        <v>154900</v>
       </c>
       <c r="H83" s="3">
-        <v>165100</v>
+        <v>147400</v>
       </c>
       <c r="I83" s="3">
-        <v>242100</v>
+        <v>207900</v>
       </c>
       <c r="J83" s="3">
-        <v>346200</v>
+        <v>285500</v>
       </c>
       <c r="K83" s="3">
         <v>389500</v>
@@ -3807,26 +3807,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-272800</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-449900</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-207100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-63800</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-185000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-158600</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-201400</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>-308900</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-120500</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-120000</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-99500</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-98300</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-180700</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-281300</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-305800</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>-293900</v>
@@ -4203,11 +4203,11 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -4221,8 +4221,8 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/SITC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SITC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>SITC</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>550900</v>
+        <v>278900</v>
       </c>
       <c r="E8" s="3">
-        <v>574600</v>
+        <v>457200</v>
       </c>
       <c r="F8" s="3">
+        <v>501500</v>
+      </c>
+      <c r="G8" s="3">
         <v>582300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>461400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>517800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>698000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>915900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1005800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1028100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>985700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>829900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>800400</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>165700</v>
+        <v>95700</v>
       </c>
       <c r="E9" s="3">
-        <v>170000</v>
+        <v>143800</v>
       </c>
       <c r="F9" s="3">
+        <v>154600</v>
+      </c>
+      <c r="G9" s="3">
         <v>152800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>138400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>139700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>208000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>263700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>277100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>293700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>281100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>239200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>233100</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>385100</v>
+        <v>183300</v>
       </c>
       <c r="E10" s="3">
-        <v>404600</v>
+        <v>313400</v>
       </c>
       <c r="F10" s="3">
+        <v>346900</v>
+      </c>
+      <c r="G10" s="3">
         <v>429500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>323000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>378200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>490000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>652200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>728700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>734400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>704600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>590800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>567300</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,93 +960,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-216500</v>
+        <v>-523900</v>
       </c>
       <c r="E14" s="3">
-        <v>-95300</v>
+        <v>-218500</v>
       </c>
       <c r="F14" s="3">
+        <v>-92800</v>
+      </c>
+      <c r="G14" s="3">
         <v>-15900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-22300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-14100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-157900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>249300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>107600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>282600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>72100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>26400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>159200</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>212500</v>
+        <v>101300</v>
       </c>
       <c r="E15" s="3">
-        <v>203500</v>
+        <v>180600</v>
       </c>
       <c r="F15" s="3">
+        <v>177000</v>
+      </c>
+      <c r="G15" s="3">
         <v>185800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>170700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>165100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>242100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>346200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>389500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>402000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>402800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>296600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>248800</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>424000</v>
+        <v>244100</v>
       </c>
       <c r="E17" s="3">
-        <v>420100</v>
+        <v>370300</v>
       </c>
       <c r="F17" s="3">
+        <v>378200</v>
+      </c>
+      <c r="G17" s="3">
         <v>393600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>362000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>363100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>507100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>669100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>850300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1051800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>840500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>641700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>717500</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>126800</v>
+        <v>34800</v>
       </c>
       <c r="E18" s="3">
-        <v>154500</v>
+        <v>86900</v>
       </c>
       <c r="F18" s="3">
+        <v>123300</v>
+      </c>
+      <c r="G18" s="3">
         <v>188700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>99500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>154700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>190800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>246800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>155500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>145100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>188200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>82900</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2100</v>
       </c>
-      <c r="E20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>18400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>110900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>68000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>51700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>33800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>115000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>50300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>124900</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>341400</v>
+        <v>131800</v>
       </c>
       <c r="E21" s="3">
-        <v>355500</v>
+        <v>269600</v>
       </c>
       <c r="F21" s="3">
+        <v>300300</v>
+      </c>
+      <c r="G21" s="3">
         <v>373300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>251800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>320200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>322000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>525000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>596700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>412200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>679200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>562600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>458900</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>82000</v>
+        <v>59500</v>
       </c>
       <c r="E22" s="3">
-        <v>77700</v>
+        <v>80500</v>
       </c>
       <c r="F22" s="3">
+        <v>76100</v>
+      </c>
+      <c r="G22" s="3">
         <v>76400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>77600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>84700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>141300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>188600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>217600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>241700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>237100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>214400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>221400</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>267800</v>
+        <v>526500</v>
       </c>
       <c r="E23" s="3">
-        <v>169600</v>
+        <v>231400</v>
       </c>
       <c r="F23" s="3">
+        <v>140000</v>
+      </c>
+      <c r="G23" s="3">
         <v>127000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>37700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>102500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>117000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-230700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-231600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>23000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>24100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13600</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>2000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>265700</v>
+        <v>525800</v>
       </c>
       <c r="E26" s="3">
-        <v>168800</v>
+        <v>229300</v>
       </c>
       <c r="F26" s="3">
+        <v>139200</v>
+      </c>
+      <c r="G26" s="3">
         <v>125400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>36600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>101800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>116100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-243100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-237900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14800</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>513700</v>
+      </c>
+      <c r="E27" s="3">
         <v>253900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>157100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>105500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>60600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>79800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-271400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-36500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-263400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-43900</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,20 +1580,23 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>36400</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>29600</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1551,23 +1611,26 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>73400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>167600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>93800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-31000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-16400</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E32" s="3">
         <v>2100</v>
       </c>
-      <c r="E32" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-18400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-110900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-68000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-51700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-33800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-115000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-50300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-124900</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>531800</v>
+      </c>
+      <c r="E33" s="3">
         <v>265700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>168700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>124900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>35700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>100700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>114400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-241700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>36900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-95800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>89600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-44500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-60300</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>531800</v>
+      </c>
+      <c r="E35" s="3">
         <v>265700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>168700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>124900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>35700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>100700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>114400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-241700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>36900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-95800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>89600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-44500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-60300</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>552000</v>
+        <v>54600</v>
       </c>
       <c r="E41" s="3">
+        <v>551400</v>
+      </c>
+      <c r="F41" s="3">
         <v>20300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>41800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>69700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>92600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>86700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>31200</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1984,51 +2073,57 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>65600</v>
+        <v>27200</v>
       </c>
       <c r="E43" s="3">
+        <v>54100</v>
+      </c>
+      <c r="F43" s="3">
         <v>63900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>61400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>73500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>68100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>121000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>187000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>121400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>129100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>132700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>129500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>126200</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2053,8 +2148,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2068,78 +2163,84 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>32600</v>
+        <v>7500</v>
       </c>
       <c r="E45" s="3">
+        <v>956100</v>
+      </c>
+      <c r="F45" s="3">
         <v>18000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>28900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12500</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>667200</v>
+        <v>102400</v>
       </c>
       <c r="E46" s="3">
+        <v>1578500</v>
+      </c>
+      <c r="F46" s="3">
         <v>103200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>116200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>159100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>97500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>144400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>297600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2152,135 +2253,147 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E47" s="3">
         <v>39400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>44600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>64600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>267300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>484600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>519600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>383800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>503600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>510300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>471100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>526300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>692300</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3278200</v>
+        <v>787800</v>
       </c>
       <c r="E48" s="3">
+        <v>2403500</v>
+      </c>
+      <c r="F48" s="3">
         <v>3798500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3686400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3582900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3442500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3455500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6294500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7247900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8065300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8426200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18147000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6968400</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>69000</v>
+        <v>12900</v>
       </c>
       <c r="E49" s="3">
+        <v>34700</v>
+      </c>
+      <c r="F49" s="3">
         <v>87700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>94100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>90400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>58000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>77400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>182400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>228700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>295100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>389200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>409600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>129300</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H52" s="3">
         <v>2300</v>
       </c>
-      <c r="E52" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2300</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>45300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>122400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>66200</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>933600</v>
+      </c>
+      <c r="E54" s="3">
         <v>4061400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4045000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3967100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4108300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4093600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4206300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7170100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8197500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9097100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9519400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9693100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8055800</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,55 +2654,59 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>112500</v>
+        <v>36900</v>
       </c>
       <c r="E57" s="3">
+        <v>125400</v>
+      </c>
+      <c r="F57" s="3">
         <v>117400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>120600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>118000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>133100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>153300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>96600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>382300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>425500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>448200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>415400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>326000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4400</v>
+        <v>5400</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2608,78 +2741,84 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>63800</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E59" s="3">
+        <v>122800</v>
+      </c>
+      <c r="F59" s="3">
         <v>30400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>44000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>45300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>78500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>75200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>68600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>61500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>55100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>44200</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>180800</v>
+        <v>42300</v>
       </c>
       <c r="E60" s="3">
+        <v>248200</v>
+      </c>
+      <c r="F60" s="3">
         <v>147800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>148800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>132800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>177200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>198600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>295800</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2692,78 +2831,84 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1659000</v>
+        <v>331500</v>
       </c>
       <c r="E61" s="3">
+        <v>1637600</v>
+      </c>
+      <c r="F61" s="3">
         <v>1744800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1715900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1973300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1888000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1884400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3849300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4494000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5139500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5212200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5294700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4319100</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>46100</v>
-      </c>
-      <c r="E62" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3">
         <v>59800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>59700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>57300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>47000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>50300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>127500</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -2776,9 +2921,12 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>416900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1885800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1952400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1924400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2163500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2112100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2133300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4272600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4960000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5641900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5749200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5788400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4713700</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,14 +3210,17 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
         <v>175000</v>
@@ -3062,19 +3229,19 @@
         <v>175000</v>
       </c>
       <c r="G70" s="3">
-        <v>325000</v>
+        <v>175000</v>
       </c>
       <c r="H70" s="3">
         <v>325000</v>
       </c>
       <c r="I70" s="3">
-        <v>525000</v>
+        <v>325000</v>
       </c>
       <c r="J70" s="3">
         <v>525000</v>
       </c>
       <c r="K70" s="3">
-        <v>350000</v>
+        <v>525000</v>
       </c>
       <c r="L70" s="3">
         <v>350000</v>
@@ -3083,14 +3250,17 @@
         <v>350000</v>
       </c>
       <c r="N70" s="3">
-        <v>405000</v>
+        <v>350000</v>
       </c>
       <c r="O70" s="3">
         <v>405000</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,9 +3300,12 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3157,24 +3330,27 @@
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>-2632300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2391800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2047200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1915600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1694800</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>516700</v>
+      </c>
+      <c r="E76" s="3">
         <v>2000500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1911800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1861900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1616500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1653400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1545100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2365900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2887500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3105200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3420200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3499700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2937100</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>531800</v>
+      </c>
+      <c r="E81" s="3">
         <v>265700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>168700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>124900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>35700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>100700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>114400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-241700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>36900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-95800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>89600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-44500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-60300</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>189800</v>
+        <v>123200</v>
       </c>
       <c r="E83" s="3">
-        <v>176000</v>
+        <v>197900</v>
       </c>
       <c r="F83" s="3">
+        <v>183600</v>
+      </c>
+      <c r="G83" s="3">
         <v>164200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>154900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>147400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>207900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>285500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>389500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>402000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>419100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>324100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>251100</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E89" s="3">
         <v>238500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>257300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>282500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>190200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>270200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>263400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>410400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>460700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>433500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>420300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>374000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>304200</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,8 +4021,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3828,24 +4048,27 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-308900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-481700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-591800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1068500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-586900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1843900</v>
+      </c>
+      <c r="E94" s="3">
         <v>559900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-167600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>74500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>102500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>818300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>478600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>473000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-54600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>153200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-897900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-588400</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,8 +4220,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4015,23 +4248,26 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-293900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-265300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-240600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-194500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-154800</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,51 +4397,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2457300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-250600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-111700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-388100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-237400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-254300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1162800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-833500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-927000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-378800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-638600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>579300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>274800</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4209,8 +4457,8 @@
       <c r="E101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>
@@ -4221,67 +4469,73 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-501400</v>
+      </c>
+      <c r="E102" s="3">
         <v>547800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-22000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-31200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>55300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-81100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>55500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-65700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>55500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SITC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SITC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>SITC</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>122900</v>
+      </c>
+      <c r="E8" s="3">
         <v>278900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>457200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>501500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>582300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>461400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>517800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>698000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>915900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1005800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1028100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>985700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>829900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>800400</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>95700</v>
+        <v>40600</v>
       </c>
       <c r="E9" s="3">
-        <v>143800</v>
+        <v>87500</v>
       </c>
       <c r="F9" s="3">
+        <v>133000</v>
+      </c>
+      <c r="G9" s="3">
         <v>154600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>152800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>138400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>139700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>208000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>263700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>277100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>293700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>281100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>239200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>233100</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>183300</v>
+        <v>82400</v>
       </c>
       <c r="E10" s="3">
-        <v>313400</v>
+        <v>191400</v>
       </c>
       <c r="F10" s="3">
+        <v>324200</v>
+      </c>
+      <c r="G10" s="3">
         <v>346900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>429500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>323000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>378200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>490000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>652200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>728700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>734400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>704600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>590800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>567300</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-195300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-526100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-219400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-94700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-15900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-22300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-14100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-157900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>249300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>107600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>282600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>72100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>26400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>159200</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E15" s="3">
         <v>101300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>180600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>177000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>185800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>170700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>165100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>242100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>346200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>389500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>402000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>402800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>296600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>248800</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E17" s="3">
         <v>244100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>370300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>378200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>393600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>362000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>363100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>507100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>669100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>850300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1051800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>840500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>641700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>717500</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E18" s="3">
         <v>34800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>86900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>123300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>188700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>99500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>154700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>190800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>246800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>155500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-23700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>145100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>188200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>82900</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E20" s="3">
         <v>6600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>18400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>110900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>68000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>51700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>33800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>115000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>50300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>124900</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E21" s="3">
         <v>129600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>268800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>298400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>373300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>251800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>320200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>322000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>525000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>596700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>412200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>679200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>562600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>458900</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E22" s="3">
         <v>59500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>80500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>76100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>76400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>77600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>84700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>141300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>188600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>217600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>241700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>237100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>214400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>221400</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>177600</v>
+      </c>
+      <c r="E23" s="3">
         <v>526500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>231400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>140000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>127000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>37700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>102500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>117000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-230700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-231600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>23000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>24100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13600</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1200</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>177900</v>
+      </c>
+      <c r="E26" s="3">
         <v>525800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>229300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>139200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>125400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>36600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>101800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>116100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-243100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-237900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>21400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>176200</v>
+      </c>
+      <c r="E27" s="3">
         <v>513700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>253900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>157100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>105500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>60600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>79800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-271400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-36500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-263400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-43900</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,24 +1640,27 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>6100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>36400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>29600</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
@@ -1614,23 +1674,26 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>73400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>167600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>93800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-31000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-18400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-110900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-68000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-51700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-33800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-115000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-50300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-124900</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>177900</v>
+      </c>
+      <c r="E33" s="3">
         <v>531800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>265700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>168700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>124900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>35700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>100700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>114400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-241700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>36900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-95800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>89600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-44500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-60300</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>177900</v>
+      </c>
+      <c r="E35" s="3">
         <v>531800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>265700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>168700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>124900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>35700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>100700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>114400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-241700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>36900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-95800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>89600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-44500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-60300</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,53 +2072,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E41" s="3">
         <v>54600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>551400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>41800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>69700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>92600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>22400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>86700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>31200</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2076,54 +2165,60 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E43" s="3">
         <v>27200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>54100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>63900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>61400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>73500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>68100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>121000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>187000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>121400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>129100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>132700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>129500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>126200</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2151,8 +2246,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2166,84 +2261,90 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E45" s="3">
         <v>7500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>956100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>26800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12500</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>143100</v>
+      </c>
+      <c r="E46" s="3">
         <v>102400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1578500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>103200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>116200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>159100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>97500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>144400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>297600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2256,144 +2357,156 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E47" s="3">
         <v>30400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>39400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>44600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>64600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>267300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>484600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>519600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>383800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>503600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>510300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>471100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>526300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>692300</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>240400</v>
+      </c>
+      <c r="E48" s="3">
         <v>787800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2403500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3798500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3686400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3582900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3442500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3455500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6294500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7247900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8065300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8426200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18147000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6968400</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E49" s="3">
         <v>12900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>34700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>87700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>94100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>90400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>58000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>77400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>182400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>228700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>295100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>389200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>409600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>129300</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,9 +2597,12 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2493,42 +2612,45 @@
       <c r="E52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>3500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>45300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>122400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>66200</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>418700</v>
+      </c>
+      <c r="E54" s="3">
         <v>933600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4061400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4045000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3967100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4108300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4093600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4206300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7170100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8197500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9097100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9519400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9693100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8055800</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,58 +2784,62 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>36900</v>
+        <v>22900</v>
       </c>
       <c r="E57" s="3">
+        <v>46200</v>
+      </c>
+      <c r="F57" s="3">
         <v>125400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>117400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>120600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>118000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>133100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>153300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>96600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>382300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>425500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>448200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>415400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>326000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5400</v>
+        <v>3800</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2744,84 +2877,90 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3">
         <v>122800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>30400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>28200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>44000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>45300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>78500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>75200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>68600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>61500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>55100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>44200</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>42300</v>
+        <v>26600</v>
       </c>
       <c r="E60" s="3">
+        <v>46200</v>
+      </c>
+      <c r="F60" s="3">
         <v>248200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>147800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>148800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>132800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>177200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>198600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>295800</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2834,84 +2973,90 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>331500</v>
+        <v>30600</v>
       </c>
       <c r="E61" s="3">
+        <v>336900</v>
+      </c>
+      <c r="F61" s="3">
         <v>1637600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1744800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1715900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1973300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1888000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1884400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3849300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4494000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5139500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5212200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5294700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4319100</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>43100</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>33800</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3">
         <v>59800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>59700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>57300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>47000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>50300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>127500</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -2924,9 +3069,12 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E66" s="3">
         <v>416900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1885800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1952400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1924400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2163500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2112100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2133300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4272600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4960000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5641900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5749200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5788400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4713700</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3223,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="F70" s="3">
         <v>175000</v>
@@ -3232,19 +3399,19 @@
         <v>175000</v>
       </c>
       <c r="H70" s="3">
-        <v>325000</v>
+        <v>175000</v>
       </c>
       <c r="I70" s="3">
         <v>325000</v>
       </c>
       <c r="J70" s="3">
-        <v>525000</v>
+        <v>325000</v>
       </c>
       <c r="K70" s="3">
         <v>525000</v>
       </c>
       <c r="L70" s="3">
-        <v>350000</v>
+        <v>525000</v>
       </c>
       <c r="M70" s="3">
         <v>350000</v>
@@ -3253,14 +3420,17 @@
         <v>350000</v>
       </c>
       <c r="O70" s="3">
-        <v>405000</v>
+        <v>350000</v>
       </c>
       <c r="P70" s="3">
         <v>405000</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>405000</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,9 +3473,12 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3333,24 +3506,27 @@
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3">
         <v>-2632300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2391800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2047200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1915600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1694800</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>334800</v>
+      </c>
+      <c r="E76" s="3">
         <v>516700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2000500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1911800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1861900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1616500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1653400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1545100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2365900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2887500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3105200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3420200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3499700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2937100</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>177900</v>
+      </c>
+      <c r="E81" s="3">
         <v>531800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>265700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>168700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>124900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>35700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>100700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>114400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-241700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>36900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-95800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>89600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-44500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-60300</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>42200</v>
+      </c>
+      <c r="E83" s="3">
         <v>123200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>197900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>183600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>164200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>154900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>147400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>207900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>285500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>389500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>402000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>419100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>324100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>251100</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E89" s="3">
         <v>112000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>238500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>257300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>282500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>190200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>270200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>263400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>410400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>460700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>433500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>420300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>374000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>304200</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,8 +4241,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4051,24 +4271,27 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3">
         <v>-308900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-481700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-591800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1068500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-586900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>705400</v>
+      </c>
+      <c r="E94" s="3">
         <v>1843900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>559900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-167600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>74500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>102500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>818300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>478600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>473000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-54600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>153200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-897900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-588400</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,8 +4453,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4251,23 +4484,26 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-293900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-265300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-240600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-194500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-154800</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,54 +4642,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-669900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2457300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-250600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-111700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-388100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-237400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-254300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1162800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-833500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-927000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-378800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-638600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>579300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>274800</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4460,8 +4708,8 @@
       <c r="F101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
@@ -4472,70 +4720,76 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>55100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-501400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>547800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-22000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-31200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>55300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-81100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>55500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-65700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>55500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
